--- a/translations/welsh-translations/10-cso-statement-start.xlsx
+++ b/translations/welsh-translations/10-cso-statement-start.xlsx
@@ -618,7 +618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -778,7 +778,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
